--- a/trabajadores_con_telefono.xlsx
+++ b/trabajadores_con_telefono.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\JM\Python\firma-cae\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5B82A6-4BB9-4E34-BCC0-7F45FB9BB27A}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D34CFB-779E-46F0-889A-4E2387C519D5}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="345" windowWidth="18105" windowHeight="9465" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>dni</t>
   </si>
@@ -182,12 +182,6 @@
     <t>607196708</t>
   </si>
   <si>
-    <t>682044960</t>
-  </si>
-  <si>
-    <t>607196743</t>
-  </si>
-  <si>
     <t>607196701</t>
   </si>
   <si>
@@ -228,13 +222,54 @@
   </si>
   <si>
     <t>028605591P</t>
+  </si>
+  <si>
+    <r>
+      <t>MARC VILA JIMENEZ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> 40374604J     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomás Aguilar Torres       </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>29505848E</t>
+    </r>
+  </si>
+  <si>
+    <t>673 35 96 15</t>
+  </si>
+  <si>
+    <t>664 78 67 03</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,6 +284,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -286,11 +333,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -629,10 +679,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -697,8 +748,8 @@
       <c r="B6" t="s">
         <v>29</v>
       </c>
-      <c r="C6" t="s">
-        <v>51</v>
+      <c r="C6">
+        <v>680112489</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -708,8 +759,8 @@
       <c r="B7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" t="s">
-        <v>52</v>
+      <c r="C7">
+        <v>610464310</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -720,7 +771,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -731,7 +782,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -742,7 +793,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -752,8 +803,8 @@
       <c r="B11" t="s">
         <v>34</v>
       </c>
-      <c r="C11" t="s">
-        <v>53</v>
+      <c r="C11">
+        <v>664786704</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,7 +815,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,7 +826,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,7 +837,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -796,8 +847,8 @@
       <c r="B15" t="s">
         <v>38</v>
       </c>
-      <c r="C15">
-        <v>616661065</v>
+      <c r="C15" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -819,7 +870,7 @@
         <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -830,7 +881,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -841,7 +892,7 @@
         <v>42</v>
       </c>
       <c r="C19">
-        <v>664500379</v>
+        <v>673359615</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,7 +903,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,7 +914,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -885,29 +936,51 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24">
-        <v>615429854</v>
+        <v>66</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="3">
+        <v>614605953</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C25">
+        <v>615429854</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26">
         <v>12345</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27">
+        <v>617828807</v>
       </c>
     </row>
   </sheetData>
